--- a/results/future_score_metrics.xlsx
+++ b/results/future_score_metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,41 +441,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RMSE</t>
+          <t>MSE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.25297414681096</v>
+        <v>105.1234788551739</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>RMSE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6852686964337404</v>
+        <v>10.25297414681096</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CV R2</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6641880334442251</v>
+        <v>0.6852686964337404</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>CV R2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6641880334442251</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Training Time</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1.749178409576416</v>
+      <c r="B7" t="n">
+        <v>1.280520915985107</v>
       </c>
     </row>
   </sheetData>

--- a/results/future_score_metrics.xlsx
+++ b/results/future_score_metrics.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.861647278362413</v>
+        <v>7.861647278362415</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.280520915985107</v>
+        <v>2.076917409896851</v>
       </c>
     </row>
   </sheetData>
